--- a/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0001T0006Z000C1N19_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0001T0006Z000C1N19_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>41.16186372410264</v>
+        <v>6.688802855166679</v>
       </c>
       <c r="D2" t="n">
-        <v>33.96128727777907</v>
+        <v>5.5187091826391</v>
       </c>
       <c r="E2" t="n">
-        <v>6.388224062806711</v>
+        <v>1.038086410206091</v>
       </c>
       <c r="F2" t="n">
-        <v>8.058819626144025</v>
+        <v>1.309558189248404</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>52.0489651709137</v>
+        <v>8.457956840273477</v>
       </c>
       <c r="D3" t="n">
-        <v>51.51815654691069</v>
+        <v>8.371700438872987</v>
       </c>
       <c r="E3" t="n">
-        <v>6.388224062806711</v>
+        <v>1.038086410206091</v>
       </c>
       <c r="F3" t="n">
-        <v>8.058819626144025</v>
+        <v>1.309558189248404</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>57.41222372093735</v>
+        <v>9.329486354652319</v>
       </c>
       <c r="D4" t="n">
-        <v>56.87373129447077</v>
+        <v>9.2419813353515</v>
       </c>
       <c r="E4" t="n">
-        <v>6.388224062806711</v>
+        <v>1.038086410206091</v>
       </c>
       <c r="F4" t="n">
-        <v>8.058819626144025</v>
+        <v>1.309558189248404</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>56.04518509451417</v>
+        <v>9.107342577858553</v>
       </c>
       <c r="D5" t="n">
-        <v>55.5221458331799</v>
+        <v>9.022348697891735</v>
       </c>
       <c r="E5" t="n">
-        <v>6.388224062806711</v>
+        <v>1.038086410206091</v>
       </c>
       <c r="F5" t="n">
-        <v>8.058819626144025</v>
+        <v>1.309558189248404</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>41.58501042479611</v>
+        <v>6.757564194029368</v>
       </c>
       <c r="D6" t="n">
-        <v>41.34247558433574</v>
+        <v>6.718152282454558</v>
       </c>
       <c r="E6" t="n">
-        <v>6.388224062806711</v>
+        <v>1.038086410206091</v>
       </c>
       <c r="F6" t="n">
-        <v>8.058819626144025</v>
+        <v>1.309558189248404</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>48.63573021829671</v>
+        <v>7.903306160473215</v>
       </c>
       <c r="D7" t="n">
-        <v>48.74589913183966</v>
+        <v>7.921208608923944</v>
       </c>
       <c r="E7" t="n">
-        <v>6.388224062806711</v>
+        <v>1.038086410206091</v>
       </c>
       <c r="F7" t="n">
-        <v>8.058819626144025</v>
+        <v>1.309558189248404</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
